--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N28_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.95859670194431</v>
+        <v>10.23077196406595</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47434209415045</v>
+        <v>3.164580590299448</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
